--- a/GOOG.xlsx
+++ b/GOOG.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\1.Finance\Anaylsen\Models\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CA40B4A8-B3C0-47BA-AFA6-8B38AC138798}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1602958C-3E3B-4C94-BD74-527B1361C643}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="19095" yWindow="0" windowWidth="19410" windowHeight="20925" activeTab="1" xr2:uid="{D4E53C97-B5F0-4187-8ABA-7D06CADAD88F}"/>
+    <workbookView xWindow="19095" yWindow="0" windowWidth="19410" windowHeight="20985" xr2:uid="{D4E53C97-B5F0-4187-8ABA-7D06CADAD88F}"/>
   </bookViews>
   <sheets>
     <sheet name="Main" sheetId="1" r:id="rId1"/>
@@ -414,13 +414,19 @@
     <numFmt numFmtId="165" formatCode="#,##0.0;\(#,##0.0\)"/>
     <numFmt numFmtId="166" formatCode="#,##0.00;\(#,##0.00\)"/>
   </numFmts>
-  <fonts count="10" x14ac:knownFonts="1">
+  <fonts count="11" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="10"/>
@@ -502,31 +508,31 @@
   </borders>
   <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
   <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="166" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="9" fontId="5" fillId="0" borderId="0" xfId="2" applyFont="1"/>
+    <xf numFmtId="9" fontId="8" fillId="0" borderId="0" xfId="2" applyFont="1"/>
+    <xf numFmtId="165" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="166" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="9" fontId="4" fillId="0" borderId="0" xfId="2" applyFont="1"/>
-    <xf numFmtId="9" fontId="7" fillId="0" borderId="0" xfId="2" applyFont="1"/>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="3" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="3" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -890,7 +896,7 @@
         <v>4</v>
       </c>
       <c r="I2" s="9">
-        <v>372.9</v>
+        <v>329.2</v>
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.2">
@@ -898,11 +904,10 @@
         <v>5</v>
       </c>
       <c r="I3" s="3">
-        <f>5824+836+5456</f>
-        <v>12116</v>
+        <v>12151</v>
       </c>
       <c r="J3" s="17" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.2">
@@ -914,7 +919,7 @@
       </c>
       <c r="I4" s="3">
         <f>I2*I3</f>
-        <v>4518056.3999999994</v>
+        <v>4000109.1999999997</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.2">
@@ -925,11 +930,11 @@
         <v>7</v>
       </c>
       <c r="I5" s="3">
-        <f>38063+88777</f>
-        <v>126840</v>
+        <f>55911+186563</f>
+        <v>242474</v>
       </c>
       <c r="J5" s="17" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.2">
@@ -940,10 +945,10 @@
         <v>8</v>
       </c>
       <c r="I6" s="3">
-        <v>77501</v>
+        <v>98165</v>
       </c>
       <c r="J6" s="17" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.2">
@@ -952,7 +957,7 @@
       </c>
       <c r="I7" s="3">
         <f>I4-I5+I6</f>
-        <v>4468717.3999999994</v>
+        <v>3855800.1999999997</v>
       </c>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.2">
@@ -1190,7 +1195,9 @@
       <c r="O3" s="3">
         <v>60399</v>
       </c>
-      <c r="P3" s="3"/>
+      <c r="P3" s="3">
+        <v>63271</v>
+      </c>
       <c r="Q3" s="3"/>
       <c r="R3" s="3"/>
       <c r="S3" s="3"/>
@@ -1321,13 +1328,15 @@
         <v>10261</v>
       </c>
       <c r="N4" s="3">
-        <f t="shared" ref="N4:O18" si="0">+Y4-SUM(K4:M4)</f>
+        <f t="shared" ref="N4:N18" si="0">+Y4-SUM(K4:M4)</f>
         <v>11383</v>
       </c>
       <c r="O4" s="3">
         <v>9883</v>
       </c>
-      <c r="P4" s="3"/>
+      <c r="P4" s="3">
+        <v>11055</v>
+      </c>
       <c r="Q4" s="3"/>
       <c r="R4" s="3"/>
       <c r="S4" s="3"/>
@@ -1464,7 +1473,9 @@
       <c r="O5" s="3">
         <v>6971</v>
       </c>
-      <c r="P5" s="3"/>
+      <c r="P5" s="3">
+        <v>7303</v>
+      </c>
       <c r="Q5" s="3"/>
       <c r="R5" s="3"/>
       <c r="S5" s="3"/>
@@ -1601,7 +1612,9 @@
       <c r="O6" s="3">
         <v>12384</v>
       </c>
-      <c r="P6" s="3"/>
+      <c r="P6" s="3">
+        <v>12911</v>
+      </c>
       <c r="Q6" s="3"/>
       <c r="R6" s="3"/>
       <c r="S6" s="3"/>
@@ -1738,7 +1751,9 @@
       <c r="O7" s="3">
         <v>20028</v>
       </c>
-      <c r="P7" s="3"/>
+      <c r="P7" s="3">
+        <v>24768</v>
+      </c>
       <c r="Q7" s="3"/>
       <c r="R7" s="3"/>
       <c r="S7" s="3"/>
@@ -1885,7 +1900,10 @@
       <c r="O8" s="3">
         <v>411</v>
       </c>
-      <c r="P8" s="3"/>
+      <c r="P8" s="3">
+        <f>382+106</f>
+        <v>488</v>
+      </c>
       <c r="Q8" s="3"/>
       <c r="R8" s="3"/>
       <c r="S8" s="3"/>
@@ -2024,7 +2042,9 @@
       <c r="O9" s="5">
         <v>109896</v>
       </c>
-      <c r="P9" s="3"/>
+      <c r="P9" s="5">
+        <v>119796</v>
+      </c>
       <c r="Q9" s="3"/>
       <c r="R9" s="3"/>
       <c r="S9" s="3"/>
@@ -2163,7 +2183,9 @@
       <c r="O10" s="3">
         <v>41271</v>
       </c>
-      <c r="P10" s="3"/>
+      <c r="P10" s="3">
+        <v>45943</v>
+      </c>
       <c r="Q10" s="3"/>
       <c r="R10" s="3"/>
       <c r="S10" s="3"/>
@@ -2314,7 +2336,10 @@
         <f>O9-O10</f>
         <v>68625</v>
       </c>
-      <c r="P11" s="3"/>
+      <c r="P11" s="3">
+        <f>P9-P10</f>
+        <v>73853</v>
+      </c>
       <c r="Q11" s="3"/>
       <c r="R11" s="3"/>
       <c r="S11" s="3"/>
@@ -2465,7 +2490,9 @@
       <c r="O12" s="3">
         <v>17032</v>
       </c>
-      <c r="P12" s="3"/>
+      <c r="P12" s="3">
+        <v>18219</v>
+      </c>
       <c r="Q12" s="3"/>
       <c r="R12" s="3"/>
       <c r="S12" s="3"/>
@@ -2604,7 +2631,9 @@
       <c r="O13" s="3">
         <v>7606</v>
       </c>
-      <c r="P13" s="3"/>
+      <c r="P13" s="3">
+        <v>8403</v>
+      </c>
       <c r="Q13" s="3"/>
       <c r="R13" s="3"/>
       <c r="S13" s="3"/>
@@ -2743,7 +2772,9 @@
       <c r="O14" s="3">
         <v>4291</v>
       </c>
-      <c r="P14" s="3"/>
+      <c r="P14" s="3">
+        <v>6461</v>
+      </c>
       <c r="Q14" s="3"/>
       <c r="R14" s="3"/>
       <c r="S14" s="3"/>
@@ -2847,7 +2878,7 @@
         <v>17415</v>
       </c>
       <c r="D15" s="3">
-        <f t="shared" ref="D15:O15" si="4">D11-SUM(D12:D14)</f>
+        <f t="shared" ref="D15:P15" si="4">D11-SUM(D12:D14)</f>
         <v>21838</v>
       </c>
       <c r="E15" s="3">
@@ -2894,7 +2925,10 @@
         <f t="shared" si="4"/>
         <v>39696</v>
       </c>
-      <c r="P15" s="3"/>
+      <c r="P15" s="3">
+        <f t="shared" si="4"/>
+        <v>40770</v>
+      </c>
       <c r="Q15" s="3"/>
       <c r="R15" s="3"/>
       <c r="S15" s="3"/>
@@ -3045,7 +3079,9 @@
       <c r="O16" s="3">
         <v>37716</v>
       </c>
-      <c r="P16" s="3"/>
+      <c r="P16" s="3">
+        <v>97983</v>
+      </c>
       <c r="Q16" s="3"/>
       <c r="R16" s="3"/>
       <c r="S16" s="3"/>
@@ -3149,7 +3185,7 @@
         <v>18205</v>
       </c>
       <c r="D17" s="3">
-        <f t="shared" ref="D17:O17" si="7">D15+D16</f>
+        <f t="shared" ref="D17:P17" si="7">D15+D16</f>
         <v>21901</v>
       </c>
       <c r="E17" s="3">
@@ -3196,7 +3232,10 @@
         <f t="shared" si="7"/>
         <v>77412</v>
       </c>
-      <c r="P17" s="3"/>
+      <c r="P17" s="3">
+        <f t="shared" si="7"/>
+        <v>138753</v>
+      </c>
       <c r="Q17" s="3"/>
       <c r="R17" s="3"/>
       <c r="S17" s="3"/>
@@ -3347,7 +3386,10 @@
       <c r="O18" s="3">
         <v>14834</v>
       </c>
-      <c r="P18" s="3"/>
+      <c r="P18" s="3">
+        <f>26560+86</f>
+        <v>26646</v>
+      </c>
       <c r="Q18" s="3"/>
       <c r="R18" s="3"/>
       <c r="S18" s="3"/>
@@ -3451,7 +3493,7 @@
         <v>15051</v>
       </c>
       <c r="D19" s="3">
-        <f t="shared" ref="D19:O19" si="10">D17-D18</f>
+        <f t="shared" ref="D19:P19" si="10">D17-D18</f>
         <v>18366</v>
       </c>
       <c r="E19" s="3">
@@ -3498,7 +3540,10 @@
         <f t="shared" si="10"/>
         <v>62578</v>
       </c>
-      <c r="P19" s="3"/>
+      <c r="P19" s="3">
+        <f t="shared" si="10"/>
+        <v>112107</v>
+      </c>
       <c r="Q19" s="3"/>
       <c r="R19" s="3"/>
       <c r="S19" s="3"/>
@@ -3738,34 +3783,37 @@
         <v>1.9135542412703557</v>
       </c>
       <c r="I21" s="6">
-        <f>+I19/I22</f>
+        <f t="shared" ref="I21:P21" si="13">+I19/I22</f>
         <v>2.1400325467860051</v>
       </c>
       <c r="J21" s="6">
-        <f>+J19/J22</f>
+        <f t="shared" si="13"/>
         <v>2.1701014066077855</v>
       </c>
       <c r="K21" s="6">
-        <f>+K19/K22</f>
+        <f t="shared" si="13"/>
         <v>2.8416289592760182</v>
       </c>
       <c r="L21" s="6">
-        <f>+L19/L22</f>
+        <f t="shared" si="13"/>
         <v>2.3260188087774294</v>
       </c>
       <c r="M21" s="6">
-        <f>+M19/M22</f>
+        <f t="shared" si="13"/>
         <v>2.8941750786033427</v>
       </c>
       <c r="N21" s="6">
-        <f>+N19/N22</f>
+        <f t="shared" si="13"/>
         <v>2.8437603169362826</v>
       </c>
       <c r="O21" s="6">
-        <f>+O19/O22</f>
+        <f t="shared" si="13"/>
         <v>5.164905909541103</v>
       </c>
-      <c r="P21" s="6"/>
+      <c r="P21" s="6">
+        <f t="shared" si="13"/>
+        <v>9.2261542259896299</v>
+      </c>
       <c r="Q21" s="6"/>
       <c r="R21" s="6"/>
       <c r="S21" s="6"/>
@@ -3773,11 +3821,11 @@
       <c r="U21" s="6"/>
       <c r="V21" s="6"/>
       <c r="W21" s="6">
-        <f t="shared" ref="W21:X21" si="13">+W19/W22</f>
+        <f t="shared" ref="W21:X21" si="14">+W19/W22</f>
         <v>5.8428345209817891</v>
       </c>
       <c r="X21" s="6">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>8.127120707849663</v>
       </c>
       <c r="Y21" s="6">
@@ -3840,9 +3888,14 @@
       <c r="N22" s="3">
         <v>12116</v>
       </c>
-      <c r="O22" s="2">
+      <c r="O22" s="3">
         <v>12116</v>
       </c>
+      <c r="P22" s="3">
+        <v>12151</v>
+      </c>
+      <c r="Q22" s="3"/>
+      <c r="R22" s="3"/>
       <c r="T22" s="3"/>
       <c r="U22" s="3"/>
       <c r="V22" s="3"/>
@@ -4023,15 +4076,15 @@
       <c r="C24" s="3"/>
       <c r="D24" s="3"/>
       <c r="G24" s="7">
-        <f t="shared" ref="G24:I30" si="14">+G3/C3-1</f>
+        <f t="shared" ref="G24:I30" si="15">+G3/C3-1</f>
         <v>0.14363586808394668</v>
       </c>
       <c r="H24" s="7">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>0.13796096462419061</v>
       </c>
       <c r="I24" s="7">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>0.12172352700676869</v>
       </c>
       <c r="J24" s="7">
@@ -4051,12 +4104,16 @@
         <v>0.14542877391920617</v>
       </c>
       <c r="N24" s="7">
-        <f t="shared" ref="N24:O30" si="15">+N3/J3-1</f>
+        <f t="shared" ref="N24:P30" si="16">+N3/J3-1</f>
         <v>0.1672835622015767</v>
       </c>
       <c r="O24" s="7">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>0.19125478284880271</v>
+      </c>
+      <c r="P24" s="7">
+        <f t="shared" si="16"/>
+        <v>0.16757704373500637</v>
       </c>
       <c r="Z24" s="13"/>
       <c r="AA24" s="13"/>
@@ -4144,40 +4201,44 @@
       <c r="C25" s="3"/>
       <c r="D25" s="3"/>
       <c r="G25" s="7">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>0.20872553414014638</v>
       </c>
       <c r="H25" s="7">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>0.13020221787345077</v>
       </c>
       <c r="I25" s="7">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>0.12185613682092544</v>
       </c>
       <c r="J25" s="7">
-        <f t="shared" ref="J25:M30" si="16">+J4/F4-1</f>
+        <f t="shared" ref="J25:M30" si="17">+J4/F4-1</f>
         <v>0.1383695652173913</v>
       </c>
       <c r="K25" s="7">
+        <f t="shared" si="17"/>
+        <v>0.10346106304079106</v>
+      </c>
+      <c r="L25" s="7">
+        <f t="shared" si="17"/>
+        <v>0.1307861018123051</v>
+      </c>
+      <c r="M25" s="7">
+        <f t="shared" si="17"/>
+        <v>0.15020737585472488</v>
+      </c>
+      <c r="N25" s="7">
         <f t="shared" si="16"/>
-        <v>0.10346106304079106</v>
-      </c>
-      <c r="L25" s="7">
+        <v>8.6890098348133327E-2</v>
+      </c>
+      <c r="O25" s="7">
         <f t="shared" si="16"/>
-        <v>0.1307861018123051</v>
-      </c>
-      <c r="M25" s="7">
+        <v>0.10709084798924606</v>
+      </c>
+      <c r="P25" s="7">
         <f t="shared" si="16"/>
-        <v>0.15020737585472488</v>
-      </c>
-      <c r="N25" s="7">
-        <f t="shared" si="15"/>
-        <v>8.6890098348133327E-2</v>
-      </c>
-      <c r="O25" s="7">
-        <f t="shared" si="15"/>
-        <v>0.10709084798924606</v>
+        <v>0.12852184565128622</v>
       </c>
       <c r="Z25" s="13"/>
       <c r="AA25" s="13"/>
@@ -4265,40 +4326,44 @@
       <c r="C26" s="3"/>
       <c r="D26" s="3"/>
       <c r="G26" s="7">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>-1.1072572038420492E-2</v>
       </c>
       <c r="H26" s="7">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>-5.1719745222929991E-2</v>
       </c>
       <c r="I26" s="7">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>-1.5777806754466051E-2</v>
       </c>
       <c r="J26" s="7">
+        <f t="shared" si="17"/>
+        <v>-4.1340243461492121E-2</v>
+      </c>
+      <c r="K26" s="7">
+        <f t="shared" si="17"/>
+        <v>-2.1179009847565045E-2</v>
+      </c>
+      <c r="L26" s="7">
+        <f t="shared" si="17"/>
+        <v>-1.2090274046211769E-2</v>
+      </c>
+      <c r="M26" s="7">
+        <f t="shared" si="17"/>
+        <v>-2.5702172760996289E-2</v>
+      </c>
+      <c r="N26" s="7">
         <f t="shared" si="16"/>
-        <v>-4.1340243461492121E-2</v>
-      </c>
-      <c r="K26" s="7">
+        <v>-1.584108624591396E-2</v>
+      </c>
+      <c r="O26" s="7">
         <f t="shared" si="16"/>
-        <v>-2.1179009847565045E-2</v>
-      </c>
-      <c r="L26" s="7">
+        <v>-3.9277839029768447E-2</v>
+      </c>
+      <c r="P26" s="7">
         <f t="shared" si="16"/>
-        <v>-1.2090274046211769E-2</v>
-      </c>
-      <c r="M26" s="7">
-        <f t="shared" si="16"/>
-        <v>-2.5702172760996289E-2</v>
-      </c>
-      <c r="N26" s="7">
-        <f t="shared" si="15"/>
-        <v>-1.584108624591396E-2</v>
-      </c>
-      <c r="O26" s="7">
-        <f t="shared" si="15"/>
-        <v>-3.9277839029768447E-2</v>
+        <v>-6.9350013598041826E-3</v>
       </c>
       <c r="Z26" s="13"/>
       <c r="AA26" s="13"/>
@@ -4386,40 +4451,44 @@
       <c r="C27" s="3"/>
       <c r="D27" s="3"/>
       <c r="G27" s="7">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>0.17887494941319293</v>
       </c>
       <c r="H27" s="7">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>0.14369933677229185</v>
       </c>
       <c r="I27" s="7">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>0.2778510612783307</v>
       </c>
       <c r="J27" s="7">
+        <f t="shared" si="17"/>
+        <v>7.772836761163604E-2</v>
+      </c>
+      <c r="K27" s="7">
+        <f t="shared" si="17"/>
+        <v>0.18766449250486317</v>
+      </c>
+      <c r="L27" s="7">
+        <f t="shared" si="17"/>
+        <v>0.20307130584192445</v>
+      </c>
+      <c r="M27" s="7">
+        <f t="shared" si="17"/>
+        <v>0.20777027027027017</v>
+      </c>
+      <c r="N27" s="7">
         <f t="shared" si="16"/>
-        <v>7.772836761163604E-2</v>
-      </c>
-      <c r="K27" s="7">
+        <v>0.1671967678156967</v>
+      </c>
+      <c r="O27" s="7">
         <f t="shared" si="16"/>
-        <v>0.18766449250486317</v>
-      </c>
-      <c r="L27" s="7">
+        <v>0.19317853357741588</v>
+      </c>
+      <c r="P27" s="7">
         <f t="shared" si="16"/>
-        <v>0.20307130584192445</v>
-      </c>
-      <c r="M27" s="7">
-        <f t="shared" si="16"/>
-        <v>0.20777027027027017</v>
-      </c>
-      <c r="N27" s="7">
-        <f t="shared" si="15"/>
-        <v>0.1671967678156967</v>
-      </c>
-      <c r="O27" s="7">
-        <f t="shared" si="15"/>
-        <v>0.19317853357741588</v>
+        <v>0.15245916272427018</v>
       </c>
       <c r="Z27" s="13"/>
       <c r="AA27" s="13"/>
@@ -4507,40 +4576,44 @@
       <c r="C28" s="3"/>
       <c r="D28" s="3"/>
       <c r="G28" s="7">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>0.28441105446740012</v>
       </c>
       <c r="H28" s="7">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>0.28838251774374291</v>
       </c>
       <c r="I28" s="7">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>0.34978004993460954</v>
       </c>
       <c r="J28" s="7">
+        <f t="shared" si="17"/>
+        <v>0.3005874673629243</v>
+      </c>
+      <c r="K28" s="7">
+        <f t="shared" si="17"/>
+        <v>0.28055149362857734</v>
+      </c>
+      <c r="L28" s="7">
+        <f t="shared" si="17"/>
+        <v>0.31671015753358467</v>
+      </c>
+      <c r="M28" s="7">
+        <f t="shared" si="17"/>
+        <v>0.33506562142165075</v>
+      </c>
+      <c r="N28" s="7">
         <f t="shared" si="16"/>
-        <v>0.3005874673629243</v>
-      </c>
-      <c r="K28" s="7">
+        <v>0.47754077791718941</v>
+      </c>
+      <c r="O28" s="7">
         <f t="shared" si="16"/>
-        <v>0.28055149362857734</v>
-      </c>
-      <c r="L28" s="7">
+        <v>0.63360522022838506</v>
+      </c>
+      <c r="P28" s="7">
         <f t="shared" si="16"/>
-        <v>0.31671015753358467</v>
-      </c>
-      <c r="M28" s="7">
-        <f t="shared" si="16"/>
-        <v>0.33506562142165075</v>
-      </c>
-      <c r="N28" s="7">
-        <f t="shared" si="15"/>
-        <v>0.47754077791718941</v>
-      </c>
-      <c r="O28" s="7">
-        <f t="shared" si="15"/>
-        <v>0.63360522022838506</v>
+        <v>0.817968291250734</v>
       </c>
       <c r="Z28" s="13"/>
       <c r="AA28" s="13"/>
@@ -4628,40 +4701,44 @@
       <c r="C29" s="3"/>
       <c r="D29" s="3"/>
       <c r="G29" s="7">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>0.52419354838709675</v>
       </c>
       <c r="H29" s="7">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>0.62152777777777768</v>
       </c>
       <c r="I29" s="7">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>0.3682432432432432</v>
       </c>
       <c r="J29" s="7">
+        <f t="shared" si="17"/>
+        <v>-0.4795539033457249</v>
+      </c>
+      <c r="K29" s="7">
+        <f t="shared" si="17"/>
+        <v>0.25220458553791891</v>
+      </c>
+      <c r="L29" s="7">
+        <f t="shared" si="17"/>
+        <v>-0.4411134903640257</v>
+      </c>
+      <c r="M29" s="7">
+        <f t="shared" si="17"/>
+        <v>-0.15061728395061724</v>
+      </c>
+      <c r="N29" s="7">
         <f t="shared" si="16"/>
-        <v>-0.4795539033457249</v>
-      </c>
-      <c r="K29" s="7">
+        <v>-0.77380952380952384</v>
+      </c>
+      <c r="O29" s="7">
         <f t="shared" si="16"/>
-        <v>0.25220458553791891</v>
-      </c>
-      <c r="L29" s="7">
+        <v>-0.42112676056338028</v>
+      </c>
+      <c r="P29" s="7">
         <f t="shared" si="16"/>
-        <v>-0.4411134903640257</v>
-      </c>
-      <c r="M29" s="7">
-        <f t="shared" si="16"/>
-        <v>-0.15061728395061724</v>
-      </c>
-      <c r="N29" s="7">
-        <f t="shared" si="15"/>
-        <v>-0.77380952380952384</v>
-      </c>
-      <c r="O29" s="7">
-        <f t="shared" si="15"/>
-        <v>-0.42112676056338028</v>
+        <v>0.86973180076628354</v>
       </c>
       <c r="Z29" s="13"/>
       <c r="AA29" s="13"/>
@@ -4749,40 +4826,44 @@
       <c r="C30" s="5"/>
       <c r="D30" s="5"/>
       <c r="G30" s="8">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>0.15406880937710454</v>
       </c>
       <c r="H30" s="8">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>0.13589083695244231</v>
       </c>
       <c r="I30" s="8">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>0.15092642092498654</v>
       </c>
       <c r="J30" s="8">
+        <f t="shared" si="17"/>
+        <v>0.11770362646275045</v>
+      </c>
+      <c r="K30" s="8">
+        <f t="shared" si="17"/>
+        <v>0.12037646357665222</v>
+      </c>
+      <c r="L30" s="8">
+        <f t="shared" si="17"/>
+        <v>0.13790092280097244</v>
+      </c>
+      <c r="M30" s="8">
+        <f t="shared" si="17"/>
+        <v>0.1594915484660353</v>
+      </c>
+      <c r="N30" s="8">
         <f t="shared" si="16"/>
-        <v>0.11770362646275045</v>
-      </c>
-      <c r="K30" s="8">
+        <v>0.17994381614819277</v>
+      </c>
+      <c r="O30" s="8">
         <f t="shared" si="16"/>
-        <v>0.12037646357665222</v>
-      </c>
-      <c r="L30" s="8">
+        <v>0.21790012633818745</v>
+      </c>
+      <c r="P30" s="8">
         <f t="shared" si="16"/>
-        <v>0.13790092280097244</v>
-      </c>
-      <c r="M30" s="8">
-        <f t="shared" si="16"/>
-        <v>0.1594915484660353</v>
-      </c>
-      <c r="N30" s="8">
-        <f t="shared" si="15"/>
-        <v>0.17994381614819277</v>
-      </c>
-      <c r="O30" s="8">
-        <f t="shared" si="15"/>
-        <v>0.21790012633818745</v>
+        <v>0.2423362508814868</v>
       </c>
       <c r="Z30" s="13"/>
       <c r="AA30" s="13"/>
@@ -4868,31 +4949,31 @@
         <v>45</v>
       </c>
       <c r="C31" s="7">
-        <f t="shared" ref="C31:I31" si="17">+C11/C9</f>
+        <f t="shared" ref="C31:I31" si="18">+C11/C9</f>
         <v>0.56135096794531936</v>
       </c>
       <c r="D31" s="7">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>0.5721945204010509</v>
       </c>
       <c r="E31" s="7">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>0.56672708069836886</v>
       </c>
       <c r="F31" s="7">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>0.56465067778936395</v>
       </c>
       <c r="G31" s="7">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>0.58142018152696207</v>
       </c>
       <c r="H31" s="7">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>0.58099879634655782</v>
       </c>
       <c r="I31" s="7">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>0.58678116644763678</v>
       </c>
       <c r="J31" s="7">
@@ -4912,12 +4993,16 @@
         <v>0.59579270318331934</v>
       </c>
       <c r="N31" s="7">
-        <f t="shared" ref="N31:O31" si="18">+N11/N9</f>
+        <f t="shared" ref="N31:O31" si="19">+N11/N9</f>
         <v>0.59793723864075621</v>
       </c>
       <c r="O31" s="7">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>0.62445402926403148</v>
+      </c>
+      <c r="P31" s="7">
+        <f t="shared" ref="P31" si="20">+P11/P9</f>
+        <v>0.61648969915523055</v>
       </c>
       <c r="Z31" s="13"/>
       <c r="AA31" s="13"/>
@@ -5003,31 +5088,31 @@
         <v>46</v>
       </c>
       <c r="C32" s="7">
-        <f t="shared" ref="C32:I32" si="19">+C15/C9</f>
+        <f t="shared" ref="C32:I32" si="21">+C15/C9</f>
         <v>0.24954504420594092</v>
       </c>
       <c r="D32" s="7">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v>0.29271888906761029</v>
       </c>
       <c r="E32" s="7">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v>0.27829136948613303</v>
       </c>
       <c r="F32" s="7">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v>0.27455683003128256</v>
       </c>
       <c r="G32" s="7">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v>0.31626913669154072</v>
       </c>
       <c r="H32" s="7">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v>0.32362936914398999</v>
       </c>
       <c r="I32" s="7">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v>0.32311823084243441</v>
       </c>
       <c r="J32" s="7">
@@ -5047,12 +5132,16 @@
         <v>0.30512184159615424</v>
       </c>
       <c r="N32" s="7">
-        <f t="shared" ref="N32:O32" si="20">+N15/N9</f>
+        <f t="shared" ref="N32:O32" si="22">+N15/N9</f>
         <v>0.31568682573707701</v>
       </c>
       <c r="O32" s="7">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v>0.36121423891679405</v>
+      </c>
+      <c r="P32" s="7">
+        <f t="shared" ref="P32" si="23">+P15/P9</f>
+        <v>0.3403285585495342</v>
       </c>
       <c r="Z32" s="13"/>
       <c r="AA32" s="13"/>
@@ -5138,31 +5227,31 @@
         <v>47</v>
       </c>
       <c r="C33" s="7">
-        <f t="shared" ref="C33:I33" si="21">+C18/C17</f>
+        <f t="shared" ref="C33:I33" si="24">+C18/C17</f>
         <v>0.17324910738808019</v>
       </c>
       <c r="D33" s="7">
-        <f t="shared" si="21"/>
+        <f t="shared" si="24"/>
         <v>0.16140815487877266</v>
       </c>
       <c r="E33" s="7">
-        <f t="shared" si="21"/>
+        <f t="shared" si="24"/>
         <v>7.1142142756050381E-2</v>
       </c>
       <c r="F33" s="7">
-        <f t="shared" si="21"/>
+        <f t="shared" si="24"/>
         <v>0.15258889070948714</v>
       </c>
       <c r="G33" s="7">
-        <f t="shared" si="21"/>
+        <f t="shared" si="24"/>
         <v>0.16432986049796927</v>
       </c>
       <c r="H33" s="7">
-        <f t="shared" si="21"/>
+        <f t="shared" si="24"/>
         <v>0.14271714275343908</v>
       </c>
       <c r="I33" s="7">
-        <f t="shared" si="21"/>
+        <f t="shared" si="24"/>
         <v>0.17047246577934777</v>
       </c>
       <c r="J33" s="7">
@@ -5182,12 +5271,16 @@
         <v>0.20478777820719757</v>
       </c>
       <c r="N33" s="7">
-        <f t="shared" ref="N33:O33" si="22">+N18/N17</f>
+        <f t="shared" ref="N33:O33" si="25">+N18/N17</f>
         <v>0.11918091878211519</v>
       </c>
       <c r="O33" s="7">
-        <f t="shared" si="22"/>
+        <f t="shared" si="25"/>
         <v>0.19162403761690694</v>
+      </c>
+      <c r="P33" s="7">
+        <f t="shared" ref="P33" si="26">+P18/P17</f>
+        <v>0.19203909104668007</v>
       </c>
       <c r="Z33" s="13"/>
       <c r="AA33" s="13"/>
@@ -10003,11 +10096,11 @@
       <c r="U77" s="5"/>
       <c r="V77" s="5"/>
       <c r="W77" s="5">
-        <f t="shared" ref="W77:X77" si="23">+SUM(W63:W68,W76)</f>
+        <f t="shared" ref="W77:X77" si="27">+SUM(W63:W68,W76)</f>
         <v>101746</v>
       </c>
       <c r="X77" s="5">
-        <f t="shared" si="23"/>
+        <f t="shared" si="27"/>
         <v>125299</v>
       </c>
       <c r="Y77" s="5">
@@ -10902,11 +10995,11 @@
       <c r="U85" s="3"/>
       <c r="V85" s="3"/>
       <c r="W85" s="5">
-        <f t="shared" ref="W85:X85" si="24">+SUM(W78:W84)</f>
+        <f t="shared" ref="W85:X85" si="28">+SUM(W78:W84)</f>
         <v>-27063</v>
       </c>
       <c r="X85" s="5">
-        <f t="shared" si="24"/>
+        <f t="shared" si="28"/>
         <v>-45536</v>
       </c>
       <c r="Y85" s="5">
@@ -11689,11 +11782,11 @@
       <c r="U92" s="5"/>
       <c r="V92" s="5"/>
       <c r="W92" s="5">
-        <f t="shared" ref="W92:X92" si="25">+SUM(W86:W91)</f>
+        <f t="shared" ref="W92:X92" si="29">+SUM(W86:W91)</f>
         <v>-72093</v>
       </c>
       <c r="X92" s="5">
-        <f t="shared" si="25"/>
+        <f t="shared" si="29"/>
         <v>-79733</v>
       </c>
       <c r="Y92" s="5">
@@ -11916,11 +12009,11 @@
       <c r="U94" s="3"/>
       <c r="V94" s="3"/>
       <c r="W94" s="5">
-        <f t="shared" ref="W94:X94" si="26">+W92+W93+W85+W77</f>
+        <f t="shared" ref="W94:X94" si="30">+W92+W93+W85+W77</f>
         <v>2169</v>
       </c>
       <c r="X94" s="5">
-        <f t="shared" si="26"/>
+        <f t="shared" si="30"/>
         <v>-582</v>
       </c>
       <c r="Y94" s="5">
